--- a/收入来源与计费逻辑.xlsx
+++ b/收入来源与计费逻辑.xlsx
@@ -32,7 +32,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +85,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -590,12 +601,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>推荐校区课时奖励收入</t>
+          <t>小时课教务推荐奖励</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>固定 5 元/课时</t>
+          <t>按上课收入比例计提，常见 1.45% / 2.9% / 3.33% / 5.8% / 6.67%，按教务人员分账</t>
         </is>
       </c>
     </row>
@@ -605,12 +616,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>间接校区课时奖励收入</t>
+          <t>小时课，校区招生服务费</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>固定 5 元/课时为主，少量 3 元/课时</t>
+          <t>按课时或金额计提，常见 80 / 58 / 15 元/课时</t>
         </is>
       </c>
     </row>
@@ -620,12 +631,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>小时课教务推荐奖励</t>
+          <t>分销补发（推荐 / 间接）</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>按上课收入比例计提，常见 1.45% / 2.9% / 3.33% / 5.8% / 6.67%，按教务人员分账</t>
+          <t>补发 2.5–10 元/条</t>
         </is>
       </c>
     </row>
@@ -635,12 +646,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>股东课时奖励收入</t>
+          <t>课程服务收入（非小时课）</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>固定 1 元/课时</t>
+          <t>固定 15 元/条</t>
         </is>
       </c>
     </row>
@@ -650,87 +661,87 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>教学校区课时奖励扣减</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>负数冲减，-0.88 至 -16.65 元，属分账修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>推荐校区课时奖励收入</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>固定 5 元/课时</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>间接校区课时奖励收入</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>固定 5 元/课时为主，少量 3 元/课时</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>股东课时奖励收入</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>固定 1 元/课时</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
           <t>理事课时奖励收入</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>固定 1 元/课时</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>小时课，校区招生服务费</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>按课时或金额计提，常见 80 / 58 / 15 元/课时</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>事业部课时奖励收入</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>固定 1 元/课时</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>分销补发（推荐 / 间接）</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>补发 2.5–10 元/条</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>课程服务收入（非小时课）</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>固定 15 元/条</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>教学校区课时奖励扣减</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>负数冲减，-0.88 至 -16.65 元，属分账修复</t>
         </is>
       </c>
     </row>
